--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A92E8D-A20E-4F20-8CF2-01F230D06BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E20184-EB5B-4262-9FBA-0A5E450A5B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1635" yWindow="-15390" windowWidth="12465" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1740" yWindow="-15180" windowWidth="10095" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
@@ -25,13 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>ID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>effectType</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -48,6 +44,27 @@
       <t>ツウジョウ</t>
     </rPh>
     <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HP10回復</t>
+    <rPh sb="4" eb="6">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>effectID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10倍攻撃</t>
+    <rPh sb="2" eb="3">
+      <t>バイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
       <t>コウゲキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -405,12 +422,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -419,13 +436,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -433,12 +450,40 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
       </c>
       <c r="D2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E20184-EB5B-4262-9FBA-0A5E450A5B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EDF22E-E395-490A-ABD5-2393085F3464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="-15180" windowWidth="10095" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9285" yWindow="-15540" windowWidth="8025" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
@@ -60,12 +60,12 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>10倍攻撃</t>
-    <rPh sb="2" eb="3">
-      <t>バイ</t>
+    <t>満腹度50回復</t>
+    <rPh sb="0" eb="3">
+      <t>マンプクド</t>
     </rPh>
-    <rPh sb="3" eb="5">
-      <t>コウゲキ</t>
+    <rPh sb="5" eb="7">
+      <t>カイフク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -426,7 +426,7 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
   </cols>
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EDF22E-E395-490A-ABD5-2393085F3464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5156E2-2531-443A-821C-A70F75C799EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9285" yWindow="-15540" windowWidth="8025" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="-15255" windowWidth="10860" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -66,6 +66,16 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10マス先に固定20ダメージ</t>
+    <rPh sb="4" eb="5">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>コテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -422,11 +432,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
   </cols>
@@ -487,6 +497,20 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5156E2-2531-443A-821C-A70F75C799EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AAB6B5-47BD-462F-A241-B943EA87DA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="-15255" windowWidth="10860" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -56,10 +65,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>effectID</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>満腹度50回復</t>
     <rPh sb="0" eb="3">
       <t>マンプクド</t>
@@ -77,6 +82,14 @@
     <rPh sb="6" eb="8">
       <t>コテイ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>effectID[]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>nameID</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -432,83 +445,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:8">
       <c r="A2" s="3">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="3">
+        <f>A2+15000</f>
+        <v>15000</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
       </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:8">
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="3">
+        <f t="shared" ref="B3:B5" si="0">A3+15000</f>
+        <v>15001</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
       </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:8">
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3">
-        <v>4</v>
+      <c r="B4" s="3">
+        <f t="shared" si="0"/>
+        <v>15002</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
       </c>
+      <c r="E4" s="3">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:8">
       <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3">
-        <v>5</v>
+      <c r="B5" s="3">
+        <f t="shared" si="0"/>
+        <v>15003</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3">
+        <v>-1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AAB6B5-47BD-462F-A241-B943EA87DA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E10B16-FA54-43A0-8FC1-2D5B0894ED72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -90,6 +90,40 @@
   </si>
   <si>
     <t>nameID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージ+焼く</t>
+    <rPh sb="5" eb="6">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満腹度30HP5</t>
+    <rPh sb="0" eb="3">
+      <t>マンプクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>満腹度30HP-5</t>
+    <rPh sb="0" eb="3">
+      <t>マンプクド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腐り攻撃予定</t>
+    <rPh sb="0" eb="1">
+      <t>クサ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨテイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -445,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -589,6 +623,114 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <f t="shared" ref="B6:B7" si="1">A6+15000</f>
+        <v>15004</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>7</v>
+      </c>
+      <c r="F6" s="3">
+        <v>6</v>
+      </c>
+      <c r="G6" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <f t="shared" si="1"/>
+        <v>15005</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>10</v>
+      </c>
+      <c r="G7" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <f t="shared" ref="B8:B9" si="2">A8+15000</f>
+        <v>15006</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <f t="shared" si="2"/>
+        <v>15007</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3">
+        <v>9</v>
+      </c>
+      <c r="G9" s="3">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/MasterData/ActionData.xlsx
+++ b/Assets/Resources/MasterData/ActionData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E10B16-FA54-43A0-8FC1-2D5B0894ED72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E83D5C1-85F7-41E8-A96A-F36B0DD1D69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-13425" windowWidth="15870" windowHeight="4350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ActionData" sheetId="1" r:id="rId1"/>
@@ -665,10 +665,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" s="3">
         <v>-1</v>
